--- a/P1278_Config_Debug.xlsx
+++ b/P1278_Config_Debug.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\PAS_Graphs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A008471C-64FF-42C6-B1B5-E83A0458B324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004EF223-6285-471E-9668-FDB04D1A4C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{18838EF4-2194-40DC-9B61-2B600CFE03D6}"/>
+    <workbookView xWindow="38290" yWindow="-330" windowWidth="38620" windowHeight="21220" xr2:uid="{18838EF4-2194-40DC-9B61-2B600CFE03D6}"/>
   </bookViews>
   <sheets>
     <sheet name="PlotConfig" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="61">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -1030,8 +1030,8 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>20</v>
+      <c r="A2">
+        <v>1278</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>21</v>
@@ -1056,8 +1056,8 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>20</v>
+      <c r="A3">
+        <v>1278</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>21</v>
@@ -1082,8 +1082,8 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>20</v>
+      <c r="A4">
+        <v>1278</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>21</v>
